--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="cfg_equip_att" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_equip_att!$A$4:$G$75</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="255">
   <si>
     <t>词条库id</t>
   </si>
@@ -38,22 +41,7 @@
     <t>词条组</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>属性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>交易行筛选词条编号</t>
@@ -245,10 +233,10 @@
     </r>
   </si>
   <si>
-    <t>201031#1#1#1000</t>
-  </si>
-  <si>
-    <t>物理攻击力</t>
+    <t>200031#1#1#1000</t>
+  </si>
+  <si>
+    <t>(攻击力/魔法/诅咒)攻击力</t>
   </si>
   <si>
     <r>
@@ -306,7 +294,7 @@
     </r>
   </si>
   <si>
-    <t>201042#200#200#1000</t>
+    <t>200042#200#200#1000</t>
   </si>
   <si>
     <r>
@@ -426,7 +414,7 @@
     </r>
   </si>
   <si>
-    <t>207042#1250#1250#1000</t>
+    <t>207041#1250#1250#1000</t>
   </si>
   <si>
     <t>击杀回复</t>
@@ -552,7 +540,1378 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>魔法攻击力</t>
+      <t>攻击每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+1</t>
+    </r>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>速度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+7</t>
+    </r>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>杀怪所获(生命值/8)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>杀怪所获(魔法值/8)</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大生命值增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +4%</t>
+    </r>
+  </si>
+  <si>
+    <t>207022#400#400#1000</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大生命值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+4%</t>
+    </r>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大魔法值增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +4%</t>
+    </r>
+  </si>
+  <si>
+    <t>208023#400#400#1000</t>
+  </si>
+  <si>
+    <t>最大魔法值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大魔法值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+4%</t>
+    </r>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害减少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +4%</t>
+    </r>
+  </si>
+  <si>
+    <t>312012#400#400#1000</t>
+  </si>
+  <si>
+    <t>伤害减少</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害减少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+4%</t>
+    </r>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害反射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <t>314012#500#500#1000</t>
+  </si>
+  <si>
+    <t>伤害反射</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害反射</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>防御成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +10%</t>
+    </r>
+  </si>
+  <si>
+    <t>211022#1000#1000#1000</t>
+  </si>
+  <si>
+    <t>防御成功率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>防御成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+10%</t>
+    </r>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杀死怪物时所获金增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +30%</t>
+    </r>
+  </si>
+  <si>
+    <t>319012#3000#3000#1000</t>
+  </si>
+  <si>
+    <t>杀怪金币加成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>杀怪所获金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+30%</t>
+    </r>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大生命增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + 200</t>
+    </r>
+  </si>
+  <si>
+    <t>207021#200#200#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大生命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+200</t>
+    </r>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能攻击力增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + 17</t>
+    </r>
+  </si>
+  <si>
+    <t>320011#17#17#1000</t>
+  </si>
+  <si>
+    <t>技能攻击力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+17</t>
+    </r>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通攻击力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法攻击力增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + 20</t>
+    </r>
+  </si>
+  <si>
+    <t>200041#20#20#1000</t>
+  </si>
+  <si>
+    <t>攻击力/魔力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法攻击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+20</t>
+    </r>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通卓越一击伤害增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + 35</t>
+    </r>
+  </si>
+  <si>
+    <t>303072#35#35#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通卓越一击伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+35</t>
+    </r>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通会心一击伤害增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> + 35</t>
+    </r>
+  </si>
+  <si>
+    <t>305072#35#35#1000</t>
+  </si>
+  <si>
+    <t>会心一击</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精通会心一击伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+35</t>
+    </r>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视敌人防御力的概率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +3%</t>
+    </r>
+  </si>
+  <si>
+    <t>317012#300#300#1000</t>
+  </si>
+  <si>
+    <t>无视防御</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视防御概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+3%</t>
+    </r>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法值增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强化等级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)*5</t>
+    </r>
+  </si>
+  <si>
+    <t>1229#50#50#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+(50+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强化等级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)*5)</t>
+    </r>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生命值增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 50+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强化等级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)*5</t>
+    </r>
+  </si>
+  <si>
+    <t>1230#50#50#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生命值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+(50+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强化等级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)*5)</t>
+    </r>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法值完全恢复几率提高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <t>329092#500#500#1000</t>
+  </si>
+  <si>
+    <t>受击概率恢复</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法值完全恢复率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全恢复生命的概率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <t>329081#500#500#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全恢复生命概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反弹攻击力几率提高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <t>500003#500#500#1000</t>
+  </si>
+  <si>
+    <t>伤害反弹</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反弹攻击几率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视敌人防御力的概率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <t>317012#500#500#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视防御概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+5%</t>
+    </r>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>166#100#1500#1000</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>168#100#1500#1000</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>170#100#1500#1000</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>172#100#1500#1000</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <t>174#100#1500#1000</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <t>176#100#1500#1000</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <t>178#100#1500#1000</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <t>180#100#1500#1000</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <t>182#100#1500#1000</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <t>184#100#1500#1000</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <t>186#100#1500#1000</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>职业增伤和减伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+  </si>
+  <si>
+    <t>188#100#1500#1000</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>1229#50#50#10000</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>1230#50#50#10000</t>
+  </si>
+  <si>
+    <t>生命值增加 50+(强化等级)*5</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全恢复生命的概率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +6%</t>
+    </r>
+  </si>
+  <si>
+    <t>329081#600#600#10000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全恢复生命的概率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 6%</t>
+    </r>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法值完全恢复几率提高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +6%</t>
+    </r>
+  </si>
+  <si>
+    <t>329092#600#600#10000</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>200042#200#200#10000</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力</t>
     </r>
     <r>
       <rPr>
@@ -592,23 +1951,20 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-  </si>
-  <si>
-    <t>202032#1#1#1000</t>
-  </si>
-  <si>
-    <t>魔法攻击力</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法攻击每</t>
+      <t xml:space="preserve"> 2.0</t>
+    </r>
+  </si>
+  <si>
+    <t>200031#2#2#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击每</t>
     </r>
     <r>
       <rPr>
@@ -632,53 +1988,189 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>+1</t>
-    </r>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法攻击力增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +2%</t>
-    </r>
-  </si>
-  <si>
-    <t>202042#200#200#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+2%</t>
-    </r>
-  </si>
-  <si>
-    <t>10</t>
+      <t>+2</t>
+    </r>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(攻击力/魔法/诅咒)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 57</t>
+    </r>
+  </si>
+  <si>
+    <t>200041#57#57#1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(攻击力/魔法/诅咒)攻击力+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>57</t>
+    </r>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>完全恢复生命概率+5%</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>双倍伤害几率 +4%</t>
+  </si>
+  <si>
+    <t>304012#400#400#100</t>
+  </si>
+  <si>
+    <t>双倍一击</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视目标防御</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> +5%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>317012#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>00#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>00#100</t>
+    </r>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>303012#1000#1000#100</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>(攻击力/魔法/诅咒)攻击力增加+等级/10</t>
+  </si>
+  <si>
+    <t>200030#1#1#100</t>
+  </si>
+  <si>
+    <t>攻击力/魔力/诅咒</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>(攻击力/魔法/诅咒)攻击力 +5%</t>
+  </si>
+  <si>
+    <t>200042#500#500#100</t>
+  </si>
+  <si>
+    <t>61</t>
   </si>
   <si>
     <r>
@@ -719,1623 +2211,6 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>速度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+7</t>
-    </r>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>杀怪所获(生命值/8)</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>杀怪所获(魔法值/8)</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大生命值增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +4%</t>
-    </r>
-  </si>
-  <si>
-    <t>207022#400#400#1000</t>
-  </si>
-  <si>
-    <t>最大生命值</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大生命值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+4%</t>
-    </r>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大魔法值增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +4%</t>
-    </r>
-  </si>
-  <si>
-    <t>208022#400#400#1000</t>
-  </si>
-  <si>
-    <t>最大魔法值</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大魔法值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+4%</t>
-    </r>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤害减少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +4%</t>
-    </r>
-  </si>
-  <si>
-    <t>312012#400#400#1000</t>
-  </si>
-  <si>
-    <t>伤害减少</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤害减少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+4%</t>
-    </r>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤害反射</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <t>314012#500#500#1000</t>
-  </si>
-  <si>
-    <t>伤害反射</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤害反射</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>防御成功率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +10%</t>
-    </r>
-  </si>
-  <si>
-    <t>211022#1000#1000#1000</t>
-  </si>
-  <si>
-    <t>防御成功率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>防御成功率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+10%</t>
-    </r>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杀死怪物时所获金增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +30%</t>
-    </r>
-  </si>
-  <si>
-    <t>319012#3000#3000#1000</t>
-  </si>
-  <si>
-    <t>杀怪金币加成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>杀怪所获金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+30%</t>
-    </r>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大生命增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> + 200</t>
-    </r>
-  </si>
-  <si>
-    <t>207021#200#200#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>最大生命</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+200</t>
-    </r>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>技能攻击力增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> + 17</t>
-    </r>
-  </si>
-  <si>
-    <t>320011#17#17#1000</t>
-  </si>
-  <si>
-    <t>技能攻击力</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>技能攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+17</t>
-    </r>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通攻击力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法攻击力增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> + 20</t>
-    </r>
-  </si>
-  <si>
-    <t>200041#20#20#1000</t>
-  </si>
-  <si>
-    <t>攻击力/魔力</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+20</t>
-    </r>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通卓越一击伤害增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> + 35</t>
-    </r>
-  </si>
-  <si>
-    <t>303072#35#35#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通卓越一击伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+35</t>
-    </r>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通会心一击伤害增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> + 35</t>
-    </r>
-  </si>
-  <si>
-    <t>305072#35#35#1000</t>
-  </si>
-  <si>
-    <t>会心一击</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精通会心一击伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+35</t>
-    </r>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无视敌人防御力的概率增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +3%</t>
-    </r>
-  </si>
-  <si>
-    <t>317012#300#300#1000</t>
-  </si>
-  <si>
-    <t>无视防御</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无视防御概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+3%</t>
-    </r>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法值增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 50+(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>强化等级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)*5</t>
-    </r>
-  </si>
-  <si>
-    <t>1229#50#50#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+(50+(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>强化等级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)*5)</t>
-    </r>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>生命值增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 50+(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>强化等级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)*5</t>
-    </r>
-  </si>
-  <si>
-    <t>1230#50#50#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>生命值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+(50+(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>强化等级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)*5)</t>
-    </r>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法值完全恢复几率提高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <t>329092#500#500#1000</t>
-  </si>
-  <si>
-    <t>受击概率恢复</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法值完全恢复率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全恢复生命的概率增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <t>329081#500#500#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全恢复生命概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反弹攻击力几率提高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <t>500003#500#500#1000</t>
-  </si>
-  <si>
-    <t>伤害反弹</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>反弹攻击几率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无视敌人防御力的概率增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <t>317012#500#500#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无视防御概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+5%</t>
-    </r>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>166#100#1500#1000</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <t>168#100#1500#1000</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>170#100#1500#1000</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <t>172#100#1500#1000</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <t>174#100#1500#1000</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <t>176#100#1500#1000</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <t>178#100#1500#1000</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <t>180#100#1500#1000</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>9</t>
-    </r>
-  </si>
-  <si>
-    <t>182#100#1500#1000</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <t>184#100#1500#1000</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <t>186#100#1500#1000</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>职业增伤和减伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12</t>
-    </r>
-  </si>
-  <si>
-    <t>188#100#1500#1000</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>1229#50#50#10000</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>1230#50#50#10000</t>
-  </si>
-  <si>
-    <t>生命值增加 50+(强化等级)*5</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全恢复生命的概率增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +6%</t>
-    </r>
-  </si>
-  <si>
-    <t>329081#600#600#10000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完全恢复生命的概率增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 6%</t>
-    </r>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法值完全恢复几率提高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +6%</t>
-    </r>
-  </si>
-  <si>
-    <t>329092#600#600#10000</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>201042#200#200#10000</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>每</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>等级增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 2.0</t>
-    </r>
-  </si>
-  <si>
-    <t>201031#2#2#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击每</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>+2</t>
-    </r>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>增加</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 57</t>
-    </r>
-  </si>
-  <si>
-    <t>201041#57#57#1000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击力+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>57</t>
-    </r>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>500126#7#7#1000</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>完全恢复生命概率+5%</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>双倍伤害几率 +4%</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>304012</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>#400#400#100</t>
-    </r>
-  </si>
-  <si>
-    <t>双倍一击</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无视目标防御</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> +5%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>317012#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>00#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>00#100</t>
-    </r>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>303012#1000#1000#100</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>(攻击力/魔法/诅咒)攻击力增加+等级/10</t>
-  </si>
-  <si>
-    <t>200030#1#1#100</t>
-  </si>
-  <si>
-    <t>攻击力/魔力/诅咒</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>(攻击力/魔法/诅咒)攻击力 +5%</t>
-  </si>
-  <si>
-    <t>200042#500#500#100</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>攻击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>魔法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>速度增加</t>
     </r>
     <r>
@@ -2348,7 +2223,7 @@
     </r>
   </si>
   <si>
-    <t>500126#10#10#100</t>
+    <t>213021#10#10#100</t>
   </si>
   <si>
     <t>62</t>
@@ -2412,7 +2287,7 @@
     <t>63</t>
   </si>
   <si>
-    <t>207042#1250#1250#100</t>
+    <t>207041#1250#1250#100</t>
   </si>
   <si>
     <t>64</t>
@@ -4088,50 +3963,50 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1">
         <v>5</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
@@ -4149,12 +4024,12 @@
         <v>38</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
@@ -4172,12 +4047,12 @@
         <v>43</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -4195,228 +4070,228 @@
         <v>43</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1">
         <v>7</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E19" s="1">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1">
         <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E22" s="1">
         <v>11</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C24">
         <v>4</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E24" s="1">
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1">
         <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -4425,492 +4300,492 @@
         <v>24</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E27" s="1">
         <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C28" s="6">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E28" s="1">
         <v>14</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E29" s="1">
         <v>7</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C31" s="6">
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E31" s="1">
         <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C32">
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E32" s="1">
         <v>15</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E33" s="1">
         <v>16</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C34">
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E34" s="1">
         <v>14</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C35">
         <v>7</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C36">
         <v>7</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C37">
         <v>7</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C38">
         <v>7</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C39">
         <v>7</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C40">
         <v>7</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C41">
         <v>7</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C42">
         <v>7</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C43">
         <v>7</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C44">
         <v>7</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C45">
         <v>7</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C46">
         <v>7</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C47">
         <v>8</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E47" s="1">
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C48">
         <v>8</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E48" s="1">
         <v>7</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G48" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C49">
         <v>8</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E49" s="1">
         <v>15</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G49" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E50" s="1">
         <v>15</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G50" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B51" t="s">
         <v>32</v>
@@ -4919,7 +4794,7 @@
         <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -4933,7 +4808,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>22</v>
@@ -4956,16 +4831,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C53">
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -4974,21 +4849,21 @@
         <v>29</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C54">
         <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -4997,12 +4872,12 @@
         <v>29</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>36</v>
@@ -5011,7 +4886,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
@@ -5025,7 +4900,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>41</v>
@@ -5043,12 +4918,12 @@
         <v>43</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>46</v>
@@ -5066,104 +4941,104 @@
         <v>43</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C58">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E58" s="1">
         <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G58" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="1" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B59" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C59">
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E59" s="1">
         <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C60">
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E60" s="1">
         <v>16</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C61">
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E61" s="1">
         <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>22</v>
@@ -5172,7 +5047,7 @@
         <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E62" s="1">
         <v>4</v>
@@ -5186,62 +5061,62 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C63">
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C64">
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C65">
         <v>11</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
@@ -5250,44 +5125,44 @@
         <v>38</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C66">
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E66" s="1">
         <v>17</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C67">
         <v>11</v>
       </c>
       <c r="D67" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E67" s="1">
         <v>3</v>
@@ -5296,21 +5171,21 @@
         <v>43</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C68">
         <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E68" s="1">
         <v>3</v>
@@ -5319,61 +5194,61 @@
         <v>43</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C69">
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E69" s="1">
         <v>6</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C70">
         <v>11</v>
       </c>
       <c r="D70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E70" s="1">
         <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G70" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C71">
         <v>12</v>
@@ -5382,93 +5257,96 @@
         <v>37</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C72">
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C73">
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C74">
         <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F74" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G74" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C75">
         <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:G75" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="D35:E46 D47:D50">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
@@ -2474,7 +2474,7 @@
     </r>
   </si>
   <si>
-    <t>207063#10#10#100</t>
+    <t>1051#10#10#100</t>
   </si>
   <si>
     <t>71</t>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_att.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_att" sheetId="1" r:id="rId1"/>
